--- a/extenbooks/S210_extenbook.xlsx
+++ b/extenbooks/S210_extenbook.xlsx
@@ -14741,7 +14741,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -15663,11 +15663,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15690,64 +15690,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>US WPI (Jastram 1977 T7 + BLS PPI extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S210_research.json", "adequacy_report": "Technical/docs/chapters/CH2_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S210_DPR.md", "epr": "Technical/docs/series/S210_EPR.md", "loader": "Technical/code/L01_loaders/L01_S210_load.py", "processor": "Technical/code/P02_processors/P02_S210_construct.py", "validator": "Technical/code/V03_validators/V03_S210_validate.py", "processed": "Technical/data/processed/S210.parquet", "chopped_csv": "Technical/chopped/S210.csv", "extenbook_xlsx": "Technical/extenbooks/S210_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S210_extenbook.xlsx
+++ b/extenbooks/S210_extenbook.xlsx
@@ -195,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$A$4:$A$250</f>
+              <f>'Data'!$A$4:$A$249</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$4:$B$250</f>
+              <f>'Data'!$B$4:$B$249</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$A$4:$A$250</f>
+              <f>'Data'!$A$4:$A$249</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$C$4:$C$250</f>
+              <f>'Data'!$C$4:$C$249</f>
             </numRef>
           </val>
         </ser>
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E745"/>
+  <dimension ref="A1:E743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
@@ -3358,60 +3358,72 @@
         <v/>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B250" t="n">
-        <v>1806.141409190946</v>
-      </c>
-      <c r="C250" t="n">
-        <v/>
-      </c>
-    </row>
+    <row r="250"/>
     <row r="251"/>
     <row r="252"/>
-    <row r="253"/>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>Long form (year, value, subseries_id, source_id, units)</t>
+        </is>
+      </c>
+    </row>
     <row r="254">
-      <c r="A254" s="1" t="inlineStr">
-        <is>
-          <t>Long form (year, value, subseries_id, source_id, units)</t>
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>subseries_id</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>units</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C255" s="3" t="inlineStr">
-        <is>
-          <t>subseries_id</t>
-        </is>
-      </c>
-      <c r="D255" s="3" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="E255" s="3" t="inlineStr">
-        <is>
-          <t>units</t>
+      <c r="A255" t="n">
+        <v>1780</v>
+      </c>
+      <c r="B255" t="n">
+        <v>115.0484798685292</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>S210-A</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>JASTRAM_1977_T7_PLUS_BLS_PPI_EXT</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>index_1930=100</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B256" t="n">
-        <v>115.0484798685292</v>
+        <v>93.21446179129006</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -3431,10 +3443,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B257" t="n">
-        <v>93.21446179129006</v>
+        <v>101.6121610517667</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -3454,10 +3466,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B258" t="n">
-        <v>101.6121610517667</v>
+        <v>89.01561216105178</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -3477,10 +3489,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B259" t="n">
-        <v>89.01561216105178</v>
+        <v>85.65653245686113</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -3500,10 +3512,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B260" t="n">
-        <v>85.65653245686113</v>
+        <v>81.45768282662286</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -3523,10 +3535,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B261" t="n">
-        <v>81.45768282662286</v>
+        <v>77.1748562037798</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -3546,10 +3558,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B262" t="n">
-        <v>77.1748562037798</v>
+        <v>75.74724732949878</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -3569,10 +3581,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B263" t="n">
-        <v>75.74724732949878</v>
+        <v>72.38816762530814</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -3592,10 +3604,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B264" t="n">
-        <v>72.38816762530814</v>
+        <v>71.71635168447001</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -3615,10 +3627,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B265" t="n">
-        <v>71.71635168447001</v>
+        <v>74.40361544782253</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -3638,10 +3650,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B266" t="n">
-        <v>74.40361544782253</v>
+        <v>76.41906327033691</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -3661,10 +3673,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B267" t="n">
-        <v>76.41906327033691</v>
+        <v>77.84667214461793</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -3684,10 +3696,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B268" t="n">
-        <v>77.84667214461793</v>
+        <v>80.53393590797043</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -3707,10 +3719,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B269" t="n">
-        <v>80.53393590797043</v>
+        <v>89.35152013147083</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -3730,10 +3742,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B270" t="n">
-        <v>89.35152013147083</v>
+        <v>102.2</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -3753,10 +3765,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B271" t="n">
-        <v>102.2</v>
+        <v>107.574527526705</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -3776,10 +3788,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B272" t="n">
-        <v>107.574527526705</v>
+        <v>103.5436318816763</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -3799,10 +3811,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B273" t="n">
-        <v>103.5436318816763</v>
+        <v>100.1005751848809</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -3822,7 +3834,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B274" t="n">
         <v>100.1005751848809</v>
@@ -3845,10 +3857,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B275" t="n">
-        <v>100.1005751848809</v>
+        <v>102.2</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -3868,10 +3880,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B276" t="n">
-        <v>102.2</v>
+        <v>112.6</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -3891,10 +3903,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B277" t="n">
-        <v>112.6</v>
+        <v>92.8</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -3914,10 +3926,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B278" t="n">
-        <v>92.8</v>
+        <v>93.5</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -3937,10 +3949,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B279" t="n">
-        <v>93.5</v>
+        <v>100</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -3960,10 +3972,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B280" t="n">
-        <v>100</v>
+        <v>111.9</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -3983,10 +3995,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B281" t="n">
-        <v>111.9</v>
+        <v>106.3</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -4006,10 +4018,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B282" t="n">
-        <v>106.3</v>
+        <v>103.1</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -4029,10 +4041,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B283" t="n">
-        <v>103.1</v>
+        <v>91.3</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -4052,10 +4064,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B284" t="n">
-        <v>91.3</v>
+        <v>103.1</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -4075,10 +4087,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B285" t="n">
-        <v>103.1</v>
+        <v>103.8</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -4098,10 +4110,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B286" t="n">
-        <v>103.8</v>
+        <v>100</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -4121,10 +4133,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B287" t="n">
-        <v>100</v>
+        <v>103.8</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -4144,10 +4156,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B288" t="n">
-        <v>103.8</v>
+        <v>128.5</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -4167,10 +4179,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B289" t="n">
-        <v>128.5</v>
+        <v>144.4</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -4190,10 +4202,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B290" t="n">
-        <v>144.4</v>
+        <v>134.8</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -4213,10 +4225,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B291" t="n">
-        <v>134.8</v>
+        <v>119.7</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -4236,7 +4248,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B292" t="n">
         <v>119.7</v>
@@ -4259,10 +4271,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B293" t="n">
-        <v>119.7</v>
+        <v>116.6</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -4282,10 +4294,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B294" t="n">
-        <v>116.6</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -4305,10 +4317,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B295" t="n">
-        <v>99.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -4328,7 +4340,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B296" t="n">
         <v>84.09999999999999</v>
@@ -4351,7 +4363,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B297" t="n">
         <v>84.09999999999999</v>
@@ -4374,10 +4386,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B298" t="n">
-        <v>84.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -4397,10 +4409,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B299" t="n">
-        <v>81.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -4420,10 +4432,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B300" t="n">
-        <v>77.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -4443,10 +4455,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B301" t="n">
-        <v>81.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -4466,10 +4478,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B302" t="n">
-        <v>78.5</v>
+        <v>77.8</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -4489,10 +4501,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B303" t="n">
-        <v>77.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -4512,10 +4524,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B304" t="n">
-        <v>76.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -4535,10 +4547,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B305" t="n">
-        <v>76.2</v>
+        <v>72.2</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -4558,10 +4570,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B306" t="n">
-        <v>72.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -4581,10 +4593,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B307" t="n">
-        <v>74.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -4604,7 +4616,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B308" t="n">
         <v>75.3</v>
@@ -4627,10 +4639,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B309" t="n">
-        <v>75.3</v>
+        <v>71.3</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -4650,10 +4662,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B310" t="n">
-        <v>71.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -4673,10 +4685,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B311" t="n">
-        <v>79.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -4696,10 +4708,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B312" t="n">
-        <v>90.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -4719,10 +4731,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B313" t="n">
-        <v>91.3</v>
+        <v>87.2</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -4742,10 +4754,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B314" t="n">
-        <v>87.2</v>
+        <v>88.8</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -4765,10 +4777,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B315" t="n">
-        <v>88.8</v>
+        <v>75.3</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -4788,10 +4800,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B316" t="n">
-        <v>75.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -4811,10 +4823,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B317" t="n">
-        <v>72.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -4834,10 +4846,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B318" t="n">
-        <v>65</v>
+        <v>59.4</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -4857,10 +4869,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B319" t="n">
-        <v>59.4</v>
+        <v>61</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -4880,10 +4892,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B320" t="n">
-        <v>61</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -4903,7 +4915,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B321" t="n">
         <v>65.90000000000001</v>
@@ -4926,10 +4938,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B322" t="n">
-        <v>65.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -4949,10 +4961,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B323" t="n">
-        <v>71.3</v>
+        <v>65</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -4972,7 +4984,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B324" t="n">
         <v>65</v>
@@ -4995,10 +5007,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B325" t="n">
-        <v>65</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -5018,10 +5030,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B326" t="n">
-        <v>66.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -5041,10 +5053,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B327" t="n">
-        <v>65.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -5064,10 +5076,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B328" t="n">
-        <v>69.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -5087,10 +5099,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B329" t="n">
-        <v>76.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -5110,10 +5122,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B330" t="n">
-        <v>85.7</v>
+        <v>87.2</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -5133,10 +5145,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B331" t="n">
-        <v>87.2</v>
+        <v>83.2</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -5156,10 +5168,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B332" t="n">
-        <v>83.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -5179,10 +5191,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B333" t="n">
-        <v>88.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -5202,10 +5214,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B334" t="n">
-        <v>73.8</v>
+        <v>76.3</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -5225,10 +5237,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B335" t="n">
-        <v>76.3</v>
+        <v>73.8</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -5248,10 +5260,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B336" t="n">
-        <v>73.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -5271,10 +5283,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B337" t="n">
-        <v>70.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -5294,10 +5306,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B338" t="n">
-        <v>82.5</v>
+        <v>105.4</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -5317,10 +5329,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B339" t="n">
-        <v>105.4</v>
+        <v>153.1</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -5340,10 +5352,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B340" t="n">
-        <v>153.1</v>
+        <v>146.6</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -5363,10 +5375,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B341" t="n">
-        <v>146.6</v>
+        <v>137.9</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -5386,10 +5398,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B342" t="n">
-        <v>137.9</v>
+        <v>128.5</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -5409,10 +5421,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B343" t="n">
-        <v>128.5</v>
+        <v>125.3</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -5432,10 +5444,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B344" t="n">
-        <v>125.3</v>
+        <v>119.7</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -5455,10 +5467,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B345" t="n">
-        <v>119.7</v>
+        <v>107</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -5478,10 +5490,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B346" t="n">
-        <v>107</v>
+        <v>103.1</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -5501,10 +5513,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B347" t="n">
-        <v>103.1</v>
+        <v>107.8</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -5524,10 +5536,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B348" t="n">
-        <v>107.8</v>
+        <v>105.4</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -5547,10 +5559,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B349" t="n">
-        <v>105.4</v>
+        <v>100</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -5570,10 +5582,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B350" t="n">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -5593,10 +5605,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B351" t="n">
-        <v>93.5</v>
+        <v>87.2</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -5616,10 +5628,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B352" t="n">
-        <v>87.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -5639,10 +5651,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B353" t="n">
-        <v>84.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -5662,10 +5674,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B354" t="n">
-        <v>72.2</v>
+        <v>71.3</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -5685,10 +5697,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B355" t="n">
-        <v>71.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -5708,10 +5720,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B356" t="n">
-        <v>79.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -5731,10 +5743,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B357" t="n">
-        <v>81.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -5754,10 +5766,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B358" t="n">
-        <v>85.7</v>
+        <v>80</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -5777,10 +5789,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B359" t="n">
-        <v>80</v>
+        <v>73.8</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -5800,10 +5812,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B360" t="n">
-        <v>73.8</v>
+        <v>67.5</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -5823,10 +5835,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B361" t="n">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -5846,10 +5858,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B362" t="n">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -5869,10 +5881,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B363" t="n">
-        <v>67.5</v>
+        <v>68.2</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -5892,10 +5904,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B364" t="n">
-        <v>68.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -5915,10 +5927,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B365" t="n">
-        <v>64.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -5938,10 +5950,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B366" t="n">
-        <v>65</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -5961,10 +5973,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B367" t="n">
-        <v>64.59999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -5984,10 +5996,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B368" t="n">
-        <v>60.3</v>
+        <v>61.9</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -6007,10 +6019,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B369" t="n">
-        <v>61.9</v>
+        <v>55.4</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -6030,10 +6042,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B370" t="n">
-        <v>55.4</v>
+        <v>56.5</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -6053,10 +6065,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B371" t="n">
-        <v>56.5</v>
+        <v>53.8</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -6076,7 +6088,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B372" t="n">
         <v>53.8</v>
@@ -6099,10 +6111,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B373" t="n">
-        <v>53.8</v>
+        <v>56.1</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -6122,10 +6134,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B374" t="n">
-        <v>56.1</v>
+        <v>60.3</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -6145,10 +6157,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B375" t="n">
-        <v>60.3</v>
+        <v>64.8</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -6168,10 +6180,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B376" t="n">
-        <v>64.8</v>
+        <v>63.9</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -6191,10 +6203,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B377" t="n">
-        <v>63.9</v>
+        <v>68.2</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -6214,10 +6226,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B378" t="n">
-        <v>68.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -6237,7 +6249,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B379" t="n">
         <v>69.09999999999999</v>
@@ -6260,10 +6272,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B380" t="n">
-        <v>69.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -6283,10 +6295,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B381" t="n">
-        <v>69.5</v>
+        <v>71.5</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -6306,10 +6318,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B382" t="n">
-        <v>71.5</v>
+        <v>75.3</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -6329,10 +6341,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B383" t="n">
-        <v>75.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -6352,10 +6364,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B384" t="n">
-        <v>72.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -6375,10 +6387,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B385" t="n">
-        <v>78.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -6398,10 +6410,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B386" t="n">
-        <v>81.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -6421,10 +6433,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B387" t="n">
-        <v>75.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -6444,10 +6456,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B388" t="n">
-        <v>80</v>
+        <v>80.7</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -6467,10 +6479,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B389" t="n">
-        <v>80.7</v>
+        <v>78.7</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -6490,10 +6502,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B390" t="n">
-        <v>78.7</v>
+        <v>80.5</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -6513,10 +6525,10 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B391" t="n">
-        <v>80.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
@@ -6536,10 +6548,10 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B392" t="n">
-        <v>98.90000000000001</v>
+        <v>135.9</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -6559,10 +6571,10 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B393" t="n">
-        <v>135.9</v>
+        <v>152</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
@@ -6582,10 +6594,10 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B394" t="n">
-        <v>152</v>
+        <v>160.3</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
@@ -6605,10 +6617,10 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B395" t="n">
-        <v>160.3</v>
+        <v>178.7</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -6628,10 +6640,10 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B396" t="n">
-        <v>178.7</v>
+        <v>113</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
@@ -6651,10 +6663,10 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B397" t="n">
-        <v>113</v>
+        <v>111.9</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -6674,10 +6686,10 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B398" t="n">
-        <v>111.9</v>
+        <v>116.4</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -6697,10 +6709,10 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B399" t="n">
-        <v>116.4</v>
+        <v>113.5</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -6720,10 +6732,10 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B400" t="n">
-        <v>113.5</v>
+        <v>119.7</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
@@ -6743,10 +6755,10 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B401" t="n">
-        <v>119.7</v>
+        <v>115.7</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
@@ -6766,10 +6778,10 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B402" t="n">
-        <v>115.7</v>
+        <v>110.5</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -6789,10 +6801,10 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B403" t="n">
-        <v>110.5</v>
+        <v>112.1</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
@@ -6812,10 +6824,10 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B404" t="n">
-        <v>112.1</v>
+        <v>110.1</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
@@ -6835,10 +6847,10 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B405" t="n">
-        <v>110.1</v>
+        <v>100</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -6858,10 +6870,10 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B406" t="n">
-        <v>100</v>
+        <v>84.3</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
@@ -6881,10 +6893,10 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B407" t="n">
-        <v>84.3</v>
+        <v>75.3</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
@@ -6904,10 +6916,10 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B408" t="n">
-        <v>75.3</v>
+        <v>76.2</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
@@ -6927,10 +6939,10 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B409" t="n">
-        <v>76.2</v>
+        <v>86.5</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -6950,10 +6962,10 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B410" t="n">
-        <v>86.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
@@ -6973,10 +6985,10 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B411" t="n">
-        <v>92.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="C411" t="inlineStr">
         <is>
@@ -6996,10 +7008,10 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B412" t="n">
-        <v>93.5</v>
+        <v>99.8</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -7019,10 +7031,10 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B413" t="n">
-        <v>99.8</v>
+        <v>90.8</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -7042,10 +7054,10 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B414" t="n">
-        <v>90.8</v>
+        <v>89.2</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
@@ -7065,10 +7077,10 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B415" t="n">
-        <v>89.2</v>
+        <v>90.8</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
@@ -7088,10 +7100,10 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B416" t="n">
-        <v>90.8</v>
+        <v>101.1</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
@@ -7111,10 +7123,10 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B417" t="n">
-        <v>101.1</v>
+        <v>114.1</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -7134,10 +7146,10 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B418" t="n">
-        <v>114.1</v>
+        <v>120.2</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
@@ -7157,7 +7169,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B419" t="n">
         <v>120.2</v>
@@ -7180,10 +7192,10 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B420" t="n">
-        <v>120.2</v>
+        <v>122.4</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
@@ -7203,10 +7215,10 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B421" t="n">
-        <v>122.4</v>
+        <v>139.7</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
@@ -7226,10 +7238,10 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B422" t="n">
-        <v>139.7</v>
+        <v>171.5</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
@@ -7249,10 +7261,10 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B423" t="n">
-        <v>171.5</v>
+        <v>185.7</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -7272,10 +7284,10 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B424" t="n">
-        <v>185.7</v>
+        <v>176.5</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -7295,10 +7307,10 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="B425" t="n">
-        <v>176.5</v>
+        <v>183.4</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
@@ -7318,10 +7330,10 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B426" t="n">
-        <v>183.4</v>
+        <v>204.3</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -7341,10 +7353,10 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="B427" t="n">
-        <v>204.3</v>
+        <v>198.7</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -7364,10 +7376,10 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B428" t="n">
-        <v>198.7</v>
+        <v>196</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
@@ -7387,10 +7399,10 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B429" t="n">
-        <v>196</v>
+        <v>196.4</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -7410,10 +7422,10 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B430" t="n">
-        <v>196.4</v>
+        <v>196.9</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
@@ -7433,10 +7445,10 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B431" t="n">
-        <v>196.9</v>
+        <v>203.4</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -7456,10 +7468,10 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B432" t="n">
-        <v>203.4</v>
+        <v>209.2</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
@@ -7479,10 +7491,10 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B433" t="n">
-        <v>209.2</v>
+        <v>212.1</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
@@ -7502,10 +7514,10 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B434" t="n">
-        <v>212.1</v>
+        <v>212.6</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
@@ -7525,7 +7537,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B435" t="n">
         <v>212.6</v>
@@ -7548,7 +7560,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B436" t="n">
         <v>212.6</v>
@@ -7571,7 +7583,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B437" t="n">
         <v>212.6</v>
@@ -7594,10 +7606,10 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B438" t="n">
-        <v>212.6</v>
+        <v>211.9</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
@@ -7617,10 +7629,10 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B439" t="n">
-        <v>211.9</v>
+        <v>212.3</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
@@ -7640,10 +7652,10 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B440" t="n">
-        <v>212.3</v>
+        <v>216.6</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
@@ -7663,10 +7675,10 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B441" t="n">
-        <v>216.6</v>
+        <v>223.8</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -7686,10 +7698,10 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B442" t="n">
-        <v>223.8</v>
+        <v>224.2</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
@@ -7709,10 +7721,10 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B443" t="n">
-        <v>224.2</v>
+        <v>229.8</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
@@ -7732,10 +7744,10 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B444" t="n">
-        <v>229.8</v>
+        <v>238.8</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
@@ -7755,10 +7767,10 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B445" t="n">
-        <v>238.8</v>
+        <v>247.5</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
@@ -7778,10 +7790,10 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B446" t="n">
-        <v>247.5</v>
+        <v>255.4</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -7801,10 +7813,10 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B447" t="n">
-        <v>255.4</v>
+        <v>267</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -7824,10 +7836,10 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B448" t="n">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -7847,10 +7859,10 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B449" t="n">
-        <v>302</v>
+        <v>359</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
@@ -7870,10 +7882,10 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B450" t="n">
-        <v>359</v>
+        <v>392.2</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
@@ -7893,10 +7905,10 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B451" t="n">
-        <v>392.2</v>
+        <v>410.2</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
@@ -7916,10 +7928,10 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B452" t="n">
-        <v>410.2</v>
+        <v>435.7116202945991</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
@@ -7939,10 +7951,10 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B453" t="n">
-        <v>435.7116202945991</v>
+        <v>469.279541734861</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
@@ -7962,10 +7974,10 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B454" t="n">
-        <v>469.279541734861</v>
+        <v>528.3590834697219</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -7985,10 +7997,10 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B455" t="n">
-        <v>528.3590834697219</v>
+        <v>602.8798690671032</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
@@ -8008,10 +8020,10 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B456" t="n">
-        <v>602.8798690671032</v>
+        <v>657.9312602291326</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
@@ -8031,10 +8043,10 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B457" t="n">
-        <v>657.9312602291326</v>
+        <v>671.3584288052374</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
@@ -8054,10 +8066,10 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B458" t="n">
-        <v>671.3584288052374</v>
+        <v>680.0860883797054</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -8077,10 +8089,10 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B459" t="n">
-        <v>680.0860883797054</v>
+        <v>696.1986906710312</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -8100,10 +8112,10 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B460" t="n">
-        <v>696.1986906710312</v>
+        <v>692.841898527005</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
@@ -8123,10 +8135,10 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B461" t="n">
-        <v>692.841898527005</v>
+        <v>672.7011456628478</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
@@ -8146,10 +8158,10 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B462" t="n">
-        <v>672.7011456628478</v>
+        <v>690.156464811784</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
@@ -8169,10 +8181,10 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B463" t="n">
-        <v>690.156464811784</v>
+        <v>717.6821603927988</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
@@ -8192,10 +8204,10 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B464" t="n">
-        <v>717.6821603927988</v>
+        <v>753.2641571194763</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -8215,10 +8227,10 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B465" t="n">
-        <v>753.2641571194763</v>
+        <v>780.7898527004909</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
@@ -8238,10 +8250,10 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B466" t="n">
-        <v>780.7898527004909</v>
+        <v>782.1325695581013</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
@@ -8261,10 +8273,10 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B467" t="n">
-        <v>782.1325695581013</v>
+        <v>786.832078559738</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
@@ -8284,10 +8296,10 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B468" t="n">
-        <v>786.832078559738</v>
+        <v>798.245171849427</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
@@ -8307,10 +8319,10 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B469" t="n">
-        <v>798.245171849427</v>
+        <v>808.3155482815056</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
@@ -8330,10 +8342,10 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B470" t="n">
-        <v>808.3155482815056</v>
+        <v>837.1839607201307</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
@@ -8353,10 +8365,10 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B471" t="n">
-        <v>837.1839607201307</v>
+        <v>857.3247135842878</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
@@ -8376,10 +8388,10 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B472" t="n">
-        <v>857.3247135842878</v>
+        <v>856.6533551554825</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
@@ -8399,10 +8411,10 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B473" t="n">
-        <v>856.6533551554825</v>
+        <v>835.169885433715</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
@@ -8422,10 +8434,10 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="B474" t="n">
-        <v>835.169885433715</v>
+        <v>842.5548281505726</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
@@ -8445,10 +8457,10 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B475" t="n">
-        <v>842.5548281505726</v>
+        <v>890.8926350245497</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
@@ -8468,10 +8480,10 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B476" t="n">
-        <v>890.8926350245497</v>
+        <v>900.9630114566282</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
@@ -8491,10 +8503,10 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B477" t="n">
-        <v>900.9630114566282</v>
+        <v>880.1509001636659</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
@@ -8514,10 +8526,10 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B478" t="n">
-        <v>880.1509001636659</v>
+        <v>927.1459901800326</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
@@ -8537,10 +8549,10 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B479" t="n">
-        <v>927.1459901800326</v>
+        <v>984.8828150572832</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
@@ -8560,10 +8572,10 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B480" t="n">
-        <v>984.8828150572832</v>
+        <v>1056.718166939444</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
@@ -8583,10 +8595,10 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B481" t="n">
-        <v>1056.718166939444</v>
+        <v>1105.727332242226</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
@@ -8606,10 +8618,10 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B482" t="n">
-        <v>1105.727332242226</v>
+        <v>1158.76464811784</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
@@ -8629,10 +8641,10 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B483" t="n">
-        <v>1158.76464811784</v>
+        <v>1272.89558101473</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
@@ -8652,10 +8664,10 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B484" t="n">
-        <v>1272.89558101473</v>
+        <v>1160.778723404256</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
@@ -8675,10 +8687,10 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B485" t="n">
-        <v>1160.778723404256</v>
+        <v>1239.999018003273</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
@@ -8698,10 +8710,10 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B486" t="n">
-        <v>1239.999018003273</v>
+        <v>1350.101800327333</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
@@ -8721,10 +8733,10 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B487" t="n">
-        <v>1350.101800327333</v>
+        <v>1357.544540087074</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
@@ -8744,10 +8756,10 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B488" t="n">
-        <v>1357.544540087074</v>
+        <v>1365.93860748528</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
@@ -8767,10 +8779,10 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B489" t="n">
-        <v>1365.93860748528</v>
+        <v>1378.753550379873</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
@@ -8790,10 +8802,10 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B490" t="n">
-        <v>1378.753550379873</v>
+        <v>1278.864148341231</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
@@ -8813,10 +8825,10 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B491" t="n">
-        <v>1278.864148341231</v>
+        <v>1244.840195153839</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -8836,10 +8848,10 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B492" t="n">
-        <v>1244.840195153839</v>
+        <v>1299.625475039458</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
@@ -8859,10 +8871,10 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B493" t="n">
-        <v>1299.625475039458</v>
+        <v>1356.14552885404</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
@@ -8882,10 +8894,10 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B494" t="n">
-        <v>1356.14552885404</v>
+        <v>1341.987535175734</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -8905,10 +8917,10 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B495" t="n">
-        <v>1341.987535175734</v>
+        <v>1305.277480420916</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -8928,10 +8940,10 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B496" t="n">
-        <v>1305.277480420916</v>
+        <v>1526.675484884525</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
@@ -8951,10 +8963,10 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B497" t="n">
-        <v>1526.675484884525</v>
+        <v>1776.057071635778</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -8974,10 +8986,10 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B498" t="n">
-        <v>1776.057071635778</v>
+        <v>1717.29132498993</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -8997,10 +9009,10 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B499" t="n">
-        <v>1717.29132498993</v>
+        <v>1709.431120278251</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
@@ -9020,10 +9032,10 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B500" t="n">
-        <v>1709.431120278251</v>
+        <v>1747.823905744161</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -9043,19 +9055,19 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>2025</v>
+        <v>1780</v>
       </c>
       <c r="B501" t="n">
-        <v>1747.823905744161</v>
+        <v>88.3</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>S210-A</t>
+          <t>S210-B</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>JASTRAM_1977_T7_PLUS_BLS_PPI_EXT</t>
+          <t>JASTRAM_1977_T2_PLUS_ONS_PLLU</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -9066,19 +9078,19 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>2026</v>
+        <v>1781</v>
       </c>
       <c r="B502" t="n">
-        <v>1806.141409190946</v>
+        <v>89.7</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>S210-A</t>
+          <t>S210-B</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>JASTRAM_1977_T7_PLUS_BLS_PPI_EXT</t>
+          <t>JASTRAM_1977_T2_PLUS_ONS_PLLU</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -9089,10 +9101,10 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="B503" t="n">
-        <v>88.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -9112,10 +9124,10 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="B504" t="n">
-        <v>89.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
@@ -9135,10 +9147,10 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="B505" t="n">
-        <v>98.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
@@ -9158,10 +9170,10 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="B506" t="n">
-        <v>95.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -9181,10 +9193,10 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B507" t="n">
-        <v>90.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
@@ -9204,10 +9216,10 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="B508" t="n">
-        <v>89.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -9227,10 +9239,10 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="B509" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -9250,10 +9262,10 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="B510" t="n">
-        <v>95.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -9273,10 +9285,10 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="B511" t="n">
-        <v>90.7</v>
+        <v>96.5</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -9296,10 +9308,10 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="B512" t="n">
-        <v>96.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
@@ -9319,10 +9331,10 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B513" t="n">
-        <v>96.5</v>
+        <v>95.2</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -9342,10 +9354,10 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="B514" t="n">
-        <v>96.90000000000001</v>
+        <v>104.4</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
@@ -9365,10 +9377,10 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="B515" t="n">
-        <v>95.2</v>
+        <v>106.4</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -9388,10 +9400,10 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="B516" t="n">
-        <v>104.4</v>
+        <v>124.1</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -9411,10 +9423,10 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B517" t="n">
-        <v>106.4</v>
+        <v>125.4</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
@@ -9434,10 +9446,10 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="B518" t="n">
-        <v>124.1</v>
+        <v>114.7</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
@@ -9457,10 +9469,10 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="B519" t="n">
-        <v>125.4</v>
+        <v>116.6</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
@@ -9480,10 +9492,10 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="B520" t="n">
-        <v>114.7</v>
+        <v>134.6</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
@@ -9503,10 +9515,10 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="B521" t="n">
-        <v>116.6</v>
+        <v>163.1</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
@@ -9526,10 +9538,10 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="B522" t="n">
-        <v>134.6</v>
+        <v>163.2</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
@@ -9549,10 +9561,10 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B523" t="n">
-        <v>163.1</v>
+        <v>132</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
@@ -9572,10 +9584,10 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="B524" t="n">
-        <v>163.2</v>
+        <v>133.5</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
@@ -9595,10 +9607,10 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="B525" t="n">
-        <v>132</v>
+        <v>134.3</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
@@ -9618,10 +9630,10 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B526" t="n">
-        <v>133.5</v>
+        <v>147.1</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
@@ -9641,10 +9653,10 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="B527" t="n">
-        <v>134.3</v>
+        <v>145.3</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
@@ -9664,10 +9676,10 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="B528" t="n">
-        <v>147.1</v>
+        <v>141.7</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
@@ -9687,10 +9699,10 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="B529" t="n">
-        <v>145.3</v>
+        <v>156.1</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
@@ -9710,10 +9722,10 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="B530" t="n">
-        <v>141.7</v>
+        <v>167.4</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
@@ -9733,10 +9745,10 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="B531" t="n">
-        <v>156.1</v>
+        <v>165.7</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
@@ -9756,10 +9768,10 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B532" t="n">
-        <v>167.4</v>
+        <v>157.1</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
@@ -9779,10 +9791,10 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="B533" t="n">
-        <v>165.7</v>
+        <v>176.8</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
@@ -9802,10 +9814,10 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="B534" t="n">
-        <v>157.1</v>
+        <v>182.5</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
@@ -9825,10 +9837,10 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="B535" t="n">
-        <v>176.8</v>
+        <v>166</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
@@ -9848,10 +9860,10 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="B536" t="n">
-        <v>182.5</v>
+        <v>140.3</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
@@ -9871,10 +9883,10 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="B537" t="n">
-        <v>166</v>
+        <v>128.1</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
@@ -9894,10 +9906,10 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="B538" t="n">
-        <v>140.3</v>
+        <v>142.9</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -9917,10 +9929,10 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="B539" t="n">
-        <v>128.1</v>
+        <v>149.8</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -9940,10 +9952,10 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="B540" t="n">
-        <v>142.9</v>
+        <v>138.4</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -9963,10 +9975,10 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="B541" t="n">
-        <v>149.8</v>
+        <v>124.7</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -9986,10 +9998,10 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B542" t="n">
-        <v>138.4</v>
+        <v>107.7</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -10009,10 +10021,10 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="B543" t="n">
-        <v>124.7</v>
+        <v>95</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -10032,10 +10044,10 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B544" t="n">
-        <v>107.7</v>
+        <v>105.4</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -10055,10 +10067,10 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="B545" t="n">
-        <v>95</v>
+        <v>110.1</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
@@ -10078,10 +10090,10 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="B546" t="n">
-        <v>105.4</v>
+        <v>122.1</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -10101,10 +10113,10 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="B547" t="n">
-        <v>110.1</v>
+        <v>108</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -10124,10 +10136,10 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="B548" t="n">
-        <v>122.1</v>
+        <v>107.3</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -10147,10 +10159,10 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="B549" t="n">
-        <v>108</v>
+        <v>104.1</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -10170,10 +10182,10 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="B550" t="n">
-        <v>107.3</v>
+        <v>103.5</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -10193,10 +10205,10 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="B551" t="n">
-        <v>104.1</v>
+        <v>102.1</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -10216,10 +10228,10 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="B552" t="n">
-        <v>103.5</v>
+        <v>102.9</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
@@ -10239,10 +10251,10 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B553" t="n">
-        <v>102.1</v>
+        <v>98.8</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -10262,10 +10274,10 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="B554" t="n">
-        <v>102.9</v>
+        <v>95.7</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
@@ -10285,10 +10297,10 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B555" t="n">
-        <v>98.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -10308,10 +10320,10 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="B556" t="n">
-        <v>95.7</v>
+        <v>91.3</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -10331,10 +10343,10 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="B557" t="n">
-        <v>93.40000000000001</v>
+        <v>102.8</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -10354,10 +10366,10 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="B558" t="n">
-        <v>91.3</v>
+        <v>101.9</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -10377,10 +10389,10 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="B559" t="n">
-        <v>102.8</v>
+        <v>105.7</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -10400,10 +10412,10 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="B560" t="n">
-        <v>101.9</v>
+        <v>112.7</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -10423,10 +10435,10 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B561" t="n">
-        <v>105.7</v>
+        <v>110.7</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -10446,10 +10458,10 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="B562" t="n">
-        <v>112.7</v>
+        <v>105.5</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
@@ -10469,10 +10481,10 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="B563" t="n">
-        <v>110.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
@@ -10492,10 +10504,10 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="B564" t="n">
-        <v>105.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="C564" t="inlineStr">
         <is>
@@ -10515,10 +10527,10 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="B565" t="n">
-        <v>95.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
@@ -10538,10 +10550,10 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B566" t="n">
-        <v>86.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
@@ -10561,10 +10573,10 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="B567" t="n">
-        <v>87.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
@@ -10584,10 +10596,10 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="B568" t="n">
-        <v>90</v>
+        <v>104.6</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
@@ -10607,10 +10619,10 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="B569" t="n">
-        <v>92.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
@@ -10630,10 +10642,10 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B570" t="n">
-        <v>104.6</v>
+        <v>79.8</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
@@ -10653,10 +10665,10 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="B571" t="n">
-        <v>88.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C571" t="inlineStr">
         <is>
@@ -10676,10 +10688,10 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="B572" t="n">
-        <v>79.8</v>
+        <v>77.3</v>
       </c>
       <c r="C572" t="inlineStr">
         <is>
@@ -10699,10 +10711,10 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="B573" t="n">
-        <v>79.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C573" t="inlineStr">
         <is>
@@ -10722,10 +10734,10 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B574" t="n">
-        <v>77.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
@@ -10745,10 +10757,10 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="B575" t="n">
-        <v>80.40000000000001</v>
+        <v>105.2</v>
       </c>
       <c r="C575" t="inlineStr">
         <is>
@@ -10768,10 +10780,10 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="B576" t="n">
-        <v>97.90000000000001</v>
+        <v>104.1</v>
       </c>
       <c r="C576" t="inlineStr">
         <is>
@@ -10791,10 +10803,10 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="B577" t="n">
-        <v>105.2</v>
+        <v>104.1</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
@@ -10814,10 +10826,10 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="B578" t="n">
-        <v>104.1</v>
+        <v>108.2</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
@@ -10837,10 +10849,10 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="B579" t="n">
-        <v>104.1</v>
+        <v>93.8</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -10860,10 +10872,10 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="B580" t="n">
-        <v>108.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -10883,10 +10895,10 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B581" t="n">
-        <v>93.8</v>
+        <v>102.1</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
@@ -10906,10 +10918,10 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="B582" t="n">
-        <v>96.90000000000001</v>
+        <v>101</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
@@ -10929,10 +10941,10 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B583" t="n">
-        <v>102.1</v>
+        <v>104.1</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -10952,10 +10964,10 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="B584" t="n">
-        <v>101</v>
+        <v>106.2</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -10975,10 +10987,10 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="B585" t="n">
-        <v>104.1</v>
+        <v>108.2</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -10998,10 +11010,10 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="B586" t="n">
-        <v>106.2</v>
+        <v>104.1</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -11021,10 +11033,10 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B587" t="n">
-        <v>108.2</v>
+        <v>105.2</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -11044,10 +11056,10 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="B588" t="n">
-        <v>104.1</v>
+        <v>103.1</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
@@ -11067,10 +11079,10 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="B589" t="n">
-        <v>105.2</v>
+        <v>102.1</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
@@ -11090,10 +11102,10 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="B590" t="n">
-        <v>103.1</v>
+        <v>101</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -11113,10 +11125,10 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="B591" t="n">
-        <v>102.1</v>
+        <v>99</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -11136,10 +11148,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="B592" t="n">
-        <v>101</v>
+        <v>103.1</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -11159,10 +11171,10 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="B593" t="n">
-        <v>99</v>
+        <v>112.4</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -11182,10 +11194,10 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B594" t="n">
-        <v>103.1</v>
+        <v>114.4</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -11205,10 +11217,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="B595" t="n">
-        <v>112.4</v>
+        <v>105.2</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -11228,10 +11240,10 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="B596" t="n">
-        <v>114.4</v>
+        <v>99</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -11251,10 +11263,10 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="B597" t="n">
-        <v>105.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -11274,10 +11286,10 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="B598" t="n">
-        <v>99</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -11297,10 +11309,10 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="B599" t="n">
-        <v>97.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -11320,10 +11332,10 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="B600" t="n">
-        <v>96.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -11343,10 +11355,10 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="B601" t="n">
-        <v>89.7</v>
+        <v>90.7</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -11366,10 +11378,10 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="B602" t="n">
-        <v>85.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -11389,10 +11401,10 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="B603" t="n">
-        <v>90.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -11412,10 +11424,10 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="B604" t="n">
-        <v>87.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -11435,10 +11447,10 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="B605" t="n">
-        <v>86.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="C605" t="inlineStr">
         <is>
@@ -11458,10 +11470,10 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="B606" t="n">
-        <v>84.5</v>
+        <v>74.2</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
@@ -11481,10 +11493,10 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="B607" t="n">
-        <v>78.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C607" t="inlineStr">
         <is>
@@ -11504,10 +11516,10 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="B608" t="n">
-        <v>74.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C608" t="inlineStr">
         <is>
@@ -11527,10 +11539,10 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="B609" t="n">
-        <v>71.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
@@ -11550,10 +11562,10 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="B610" t="n">
-        <v>70.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="C610" t="inlineStr">
         <is>
@@ -11573,10 +11585,10 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="B611" t="n">
-        <v>72.2</v>
+        <v>74.2</v>
       </c>
       <c r="C611" t="inlineStr">
         <is>
@@ -11596,7 +11608,7 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="B612" t="n">
         <v>74.2</v>
@@ -11619,10 +11631,10 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="B613" t="n">
-        <v>74.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C613" t="inlineStr">
         <is>
@@ -11642,10 +11654,10 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="B614" t="n">
-        <v>74.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
@@ -11665,10 +11677,10 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="B615" t="n">
-        <v>70.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C615" t="inlineStr">
         <is>
@@ -11688,10 +11700,10 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="B616" t="n">
-        <v>70.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="C616" t="inlineStr">
         <is>
@@ -11711,10 +11723,10 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="B617" t="n">
-        <v>64.90000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
@@ -11734,7 +11746,7 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="B618" t="n">
         <v>63.9</v>
@@ -11757,10 +11769,10 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="B619" t="n">
-        <v>62.9</v>
+        <v>66</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
@@ -11780,10 +11792,10 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="B620" t="n">
-        <v>63.9</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="C620" t="inlineStr">
         <is>
@@ -11803,10 +11815,10 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="B621" t="n">
-        <v>66</v>
+        <v>77.3</v>
       </c>
       <c r="C621" t="inlineStr">
         <is>
@@ -11826,10 +11838,10 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="B622" t="n">
-        <v>70.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C622" t="inlineStr">
         <is>
@@ -11849,10 +11861,10 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="B623" t="n">
-        <v>77.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="C623" t="inlineStr">
         <is>
@@ -11872,10 +11884,10 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="B624" t="n">
-        <v>72.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
@@ -11895,10 +11907,10 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="B625" t="n">
-        <v>71.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
@@ -11918,10 +11930,10 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="B626" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
@@ -11941,10 +11953,10 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="B627" t="n">
-        <v>72.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C627" t="inlineStr">
         <is>
@@ -11964,10 +11976,10 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="B628" t="n">
-        <v>74.2</v>
+        <v>82.5</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
@@ -11987,10 +11999,10 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="B629" t="n">
-        <v>79.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
@@ -12010,10 +12022,10 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="B630" t="n">
-        <v>82.5</v>
+        <v>76.3</v>
       </c>
       <c r="C630" t="inlineStr">
         <is>
@@ -12033,10 +12045,10 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="B631" t="n">
-        <v>75.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="C631" t="inlineStr">
         <is>
@@ -12056,10 +12068,10 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="B632" t="n">
-        <v>76.3</v>
+        <v>82.5</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
@@ -12079,10 +12091,10 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B633" t="n">
-        <v>80.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="C633" t="inlineStr">
         <is>
@@ -12102,10 +12114,10 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="B634" t="n">
-        <v>82.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="C634" t="inlineStr">
         <is>
@@ -12125,7 +12137,7 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="B635" t="n">
         <v>87.59999999999999</v>
@@ -12148,10 +12160,10 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="B636" t="n">
-        <v>87.59999999999999</v>
+        <v>111.3</v>
       </c>
       <c r="C636" t="inlineStr">
         <is>
@@ -12171,10 +12183,10 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="B637" t="n">
-        <v>87.59999999999999</v>
+        <v>140.2</v>
       </c>
       <c r="C637" t="inlineStr">
         <is>
@@ -12194,10 +12206,10 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="B638" t="n">
-        <v>111.3</v>
+        <v>184.5</v>
       </c>
       <c r="C638" t="inlineStr">
         <is>
@@ -12217,10 +12229,10 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="B639" t="n">
-        <v>140.2</v>
+        <v>197.9</v>
       </c>
       <c r="C639" t="inlineStr">
         <is>
@@ -12240,10 +12252,10 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="B640" t="n">
-        <v>184.5</v>
+        <v>212.4</v>
       </c>
       <c r="C640" t="inlineStr">
         <is>
@@ -12263,10 +12275,10 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="B641" t="n">
-        <v>197.9</v>
+        <v>258.8</v>
       </c>
       <c r="C641" t="inlineStr">
         <is>
@@ -12286,10 +12298,10 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="B642" t="n">
-        <v>212.4</v>
+        <v>159.8</v>
       </c>
       <c r="C642" t="inlineStr">
         <is>
@@ -12309,10 +12321,10 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="B643" t="n">
-        <v>258.8</v>
+        <v>135.1</v>
       </c>
       <c r="C643" t="inlineStr">
         <is>
@@ -12332,10 +12344,10 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="B644" t="n">
-        <v>159.8</v>
+        <v>133</v>
       </c>
       <c r="C644" t="inlineStr">
         <is>
@@ -12355,10 +12367,10 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="B645" t="n">
-        <v>135.1</v>
+        <v>143.3</v>
       </c>
       <c r="C645" t="inlineStr">
         <is>
@@ -12378,10 +12390,10 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="B646" t="n">
-        <v>133</v>
+        <v>140.2</v>
       </c>
       <c r="C646" t="inlineStr">
         <is>
@@ -12401,10 +12413,10 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="B647" t="n">
-        <v>143.3</v>
+        <v>129.9</v>
       </c>
       <c r="C647" t="inlineStr">
         <is>
@@ -12424,10 +12436,10 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B648" t="n">
-        <v>140.2</v>
+        <v>125.8</v>
       </c>
       <c r="C648" t="inlineStr">
         <is>
@@ -12447,10 +12459,10 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="B649" t="n">
-        <v>129.9</v>
+        <v>123.7</v>
       </c>
       <c r="C649" t="inlineStr">
         <is>
@@ -12470,10 +12482,10 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="B650" t="n">
-        <v>125.8</v>
+        <v>118.8</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
@@ -12493,10 +12505,10 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="B651" t="n">
-        <v>123.7</v>
+        <v>100</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
@@ -12516,10 +12528,10 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="B652" t="n">
-        <v>118.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
@@ -12539,10 +12551,10 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="B653" t="n">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="C653" t="inlineStr">
         <is>
@@ -12562,10 +12574,10 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="B654" t="n">
-        <v>85.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C654" t="inlineStr">
         <is>
@@ -12585,10 +12597,10 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="B655" t="n">
-        <v>82.5</v>
+        <v>84.5</v>
       </c>
       <c r="C655" t="inlineStr">
         <is>
@@ -12608,10 +12620,10 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="B656" t="n">
-        <v>81.40000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="C656" t="inlineStr">
         <is>
@@ -12631,10 +12643,10 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="B657" t="n">
-        <v>84.5</v>
+        <v>91.8</v>
       </c>
       <c r="C657" t="inlineStr">
         <is>
@@ -12654,10 +12666,10 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="B658" t="n">
-        <v>86.59999999999999</v>
+        <v>105.2</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
@@ -12677,10 +12689,10 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="B659" t="n">
-        <v>91.8</v>
+        <v>93.8</v>
       </c>
       <c r="C659" t="inlineStr">
         <is>
@@ -12700,10 +12712,10 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="B660" t="n">
-        <v>105.2</v>
+        <v>98.7507930720146</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
@@ -12723,10 +12735,10 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="B661" t="n">
-        <v>93.8</v>
+        <v>132.3289699179583</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
@@ -12746,10 +12758,10 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="B662" t="n">
-        <v>98.7507930720146</v>
+        <v>146.1980309936186</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
@@ -12769,10 +12781,10 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="B663" t="n">
-        <v>132.3289699179583</v>
+        <v>155.962807657247</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
@@ -12792,10 +12804,10 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="B664" t="n">
-        <v>146.1980309936186</v>
+        <v>158.4339288969914</v>
       </c>
       <c r="C664" t="inlineStr">
         <is>
@@ -12815,10 +12827,10 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="B665" t="n">
-        <v>155.962807657247</v>
+        <v>163.0769006381035</v>
       </c>
       <c r="C665" t="inlineStr">
         <is>
@@ -12838,10 +12850,10 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="B666" t="n">
-        <v>158.4339288969914</v>
+        <v>167.4120510483132</v>
       </c>
       <c r="C666" t="inlineStr">
         <is>
@@ -12861,10 +12873,10 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B667" t="n">
-        <v>163.0769006381035</v>
+        <v>162</v>
       </c>
       <c r="C667" t="inlineStr">
         <is>
@@ -12884,10 +12896,10 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="B668" t="n">
-        <v>167.4120510483132</v>
+        <v>177.4</v>
       </c>
       <c r="C668" t="inlineStr">
         <is>
@@ -12907,10 +12919,10 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B669" t="n">
-        <v>162</v>
+        <v>202.8</v>
       </c>
       <c r="C669" t="inlineStr">
         <is>
@@ -12930,10 +12942,10 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="B670" t="n">
-        <v>177.4</v>
+        <v>212.7</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
@@ -12953,10 +12965,10 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="B671" t="n">
-        <v>202.8</v>
+        <v>248</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
@@ -12976,10 +12988,10 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="B672" t="n">
-        <v>212.7</v>
+        <v>365.7</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
@@ -12999,10 +13011,10 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="B673" t="n">
-        <v>248</v>
+        <v>375.1</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
@@ -13022,10 +13034,10 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="B674" t="n">
-        <v>365.7</v>
+        <v>375.5</v>
       </c>
       <c r="C674" t="inlineStr">
         <is>
@@ -13045,10 +13057,10 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="B675" t="n">
-        <v>375.1</v>
+        <v>377.8</v>
       </c>
       <c r="C675" t="inlineStr">
         <is>
@@ -13068,10 +13080,10 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="B676" t="n">
-        <v>375.5</v>
+        <v>389.4</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
@@ -13091,10 +13103,10 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="B677" t="n">
-        <v>377.8</v>
+        <v>406.1</v>
       </c>
       <c r="C677" t="inlineStr">
         <is>
@@ -13114,10 +13126,10 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="B678" t="n">
-        <v>389.4</v>
+        <v>419</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
@@ -13137,10 +13149,10 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="B679" t="n">
-        <v>406.1</v>
+        <v>421.7</v>
       </c>
       <c r="C679" t="inlineStr">
         <is>
@@ -13160,10 +13172,10 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="B680" t="n">
-        <v>419</v>
+        <v>423.2</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
@@ -13183,10 +13195,10 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="B681" t="n">
-        <v>421.7</v>
+        <v>428.9</v>
       </c>
       <c r="C681" t="inlineStr">
         <is>
@@ -13206,10 +13218,10 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="B682" t="n">
-        <v>423.2</v>
+        <v>440.3</v>
       </c>
       <c r="C682" t="inlineStr">
         <is>
@@ -13229,10 +13241,10 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="B683" t="n">
-        <v>428.9</v>
+        <v>450.1</v>
       </c>
       <c r="C683" t="inlineStr">
         <is>
@@ -13252,10 +13264,10 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="B684" t="n">
-        <v>440.3</v>
+        <v>456.2</v>
       </c>
       <c r="C684" t="inlineStr">
         <is>
@@ -13275,10 +13287,10 @@
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="B685" t="n">
-        <v>450.1</v>
+        <v>471.4</v>
       </c>
       <c r="C685" t="inlineStr">
         <is>
@@ -13298,10 +13310,10 @@
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="B686" t="n">
-        <v>456.2</v>
+        <v>493.1</v>
       </c>
       <c r="C686" t="inlineStr">
         <is>
@@ -13321,10 +13333,10 @@
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="B687" t="n">
-        <v>471.4</v>
+        <v>506.8</v>
       </c>
       <c r="C687" t="inlineStr">
         <is>
@@ -13344,10 +13356,10 @@
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="B688" t="n">
-        <v>493.1</v>
+        <v>513.3</v>
       </c>
       <c r="C688" t="inlineStr">
         <is>
@@ -13367,10 +13379,10 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="B689" t="n">
-        <v>506.8</v>
+        <v>536.1</v>
       </c>
       <c r="C689" t="inlineStr">
         <is>
@@ -13390,10 +13402,10 @@
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="B690" t="n">
-        <v>513.3</v>
+        <v>557</v>
       </c>
       <c r="C690" t="inlineStr">
         <is>
@@ -13413,10 +13425,10 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="B691" t="n">
-        <v>536.1</v>
+        <v>596.3</v>
       </c>
       <c r="C691" t="inlineStr">
         <is>
@@ -13436,10 +13448,10 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B692" t="n">
-        <v>557</v>
+        <v>650</v>
       </c>
       <c r="C692" t="inlineStr">
         <is>
@@ -13459,10 +13471,10 @@
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="B693" t="n">
-        <v>596.3</v>
+        <v>684.6</v>
       </c>
       <c r="C693" t="inlineStr">
         <is>
@@ -13482,10 +13494,10 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B694" t="n">
-        <v>650</v>
+        <v>734.7</v>
       </c>
       <c r="C694" t="inlineStr">
         <is>
@@ -13505,10 +13517,10 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="B695" t="n">
-        <v>684.6</v>
+        <v>906.4</v>
       </c>
       <c r="C695" t="inlineStr">
         <is>
@@ -13528,10 +13540,10 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B696" t="n">
-        <v>734.7</v>
+        <v>1125.3</v>
       </c>
       <c r="C696" t="inlineStr">
         <is>
@@ -13551,10 +13563,10 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="B697" t="n">
-        <v>906.4</v>
+        <v>1248.4</v>
       </c>
       <c r="C697" t="inlineStr">
         <is>
@@ -13574,10 +13586,10 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B698" t="n">
-        <v>1125.3</v>
+        <v>1475.821705426357</v>
       </c>
       <c r="C698" t="inlineStr">
         <is>
@@ -13597,10 +13609,10 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="B699" t="n">
-        <v>1248.4</v>
+        <v>1620.984496124031</v>
       </c>
       <c r="C699" t="inlineStr">
         <is>
@@ -13620,10 +13632,10 @@
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="B700" t="n">
-        <v>1475.821705426357</v>
+        <v>1797.599224806201</v>
       </c>
       <c r="C700" t="inlineStr">
         <is>
@@ -13643,10 +13655,10 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="B701" t="n">
-        <v>1620.984496124031</v>
+        <v>2049.214728682171</v>
       </c>
       <c r="C701" t="inlineStr">
         <is>
@@ -13666,10 +13678,10 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B702" t="n">
-        <v>1797.599224806201</v>
+        <v>2245.184496124032</v>
       </c>
       <c r="C702" t="inlineStr">
         <is>
@@ -13689,10 +13701,10 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B703" t="n">
-        <v>2049.214728682171</v>
+        <v>2419.37984496124</v>
       </c>
       <c r="C703" t="inlineStr">
         <is>
@@ -13712,10 +13724,10 @@
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B704" t="n">
-        <v>2245.184496124032</v>
+        <v>2550.026356589148</v>
       </c>
       <c r="C704" t="inlineStr">
         <is>
@@ -13735,10 +13747,10 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B705" t="n">
-        <v>2419.37984496124</v>
+        <v>2674.531015051315</v>
       </c>
       <c r="C705" t="inlineStr">
         <is>
@@ -13758,10 +13770,10 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B706" t="n">
-        <v>2550.026356589148</v>
+        <v>2840.351937984496</v>
       </c>
       <c r="C706" t="inlineStr">
         <is>
@@ -13781,10 +13793,10 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B707" t="n">
-        <v>2674.531015051315</v>
+        <v>2880.11686511628</v>
       </c>
       <c r="C707" t="inlineStr">
         <is>
@@ -13804,10 +13816,10 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B708" t="n">
-        <v>2840.351937984496</v>
+        <v>2978.040838530233</v>
       </c>
       <c r="C708" t="inlineStr">
         <is>
@@ -13827,10 +13839,10 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B709" t="n">
-        <v>2880.11686511628</v>
+        <v>3088.228349555853</v>
       </c>
       <c r="C709" t="inlineStr">
         <is>
@@ -13850,10 +13862,10 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B710" t="n">
-        <v>2978.040838530233</v>
+        <v>3236.463310334534</v>
       </c>
       <c r="C710" t="inlineStr">
         <is>
@@ -13873,10 +13885,10 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="B711" t="n">
-        <v>3088.228349555853</v>
+        <v>3437.124035575274</v>
       </c>
       <c r="C711" t="inlineStr">
         <is>
@@ -13896,10 +13908,10 @@
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="B712" t="n">
-        <v>3236.463310334534</v>
+        <v>3622.72873349634</v>
       </c>
       <c r="C712" t="inlineStr">
         <is>
@@ -13919,10 +13931,10 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="B713" t="n">
-        <v>3437.124035575274</v>
+        <v>3735.033324234726</v>
       </c>
       <c r="C713" t="inlineStr">
         <is>
@@ -13942,10 +13954,10 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="B714" t="n">
-        <v>3622.72873349634</v>
+        <v>3883.068181597687</v>
       </c>
       <c r="C714" t="inlineStr">
         <is>
@@ -13965,10 +13977,10 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="B715" t="n">
-        <v>3735.033324234726</v>
+        <v>3980.377808115998</v>
       </c>
       <c r="C715" t="inlineStr">
         <is>
@@ -13988,10 +14000,10 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="B716" t="n">
-        <v>3883.068181597687</v>
+        <v>4140.835170991935</v>
       </c>
       <c r="C716" t="inlineStr">
         <is>
@@ -14011,10 +14023,10 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B717" t="n">
-        <v>3980.377808115998</v>
+        <v>4248.828152251405</v>
       </c>
       <c r="C717" t="inlineStr">
         <is>
@@ -14034,10 +14046,10 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="B718" t="n">
-        <v>4140.835170991935</v>
+        <v>4286.799610769401</v>
       </c>
       <c r="C718" t="inlineStr">
         <is>
@@ -14057,10 +14069,10 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="B719" t="n">
-        <v>4248.828152251405</v>
+        <v>4311.313354981674</v>
       </c>
       <c r="C719" t="inlineStr">
         <is>
@@ -14080,10 +14092,10 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="B720" t="n">
-        <v>4286.799610769401</v>
+        <v>4360.299435054508</v>
       </c>
       <c r="C720" t="inlineStr">
         <is>
@@ -14103,10 +14115,10 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B721" t="n">
-        <v>4311.313354981674</v>
+        <v>4470.735509064863</v>
       </c>
       <c r="C721" t="inlineStr">
         <is>
@@ -14126,10 +14138,10 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="B722" t="n">
-        <v>4360.299435054508</v>
+        <v>4480.383655013275</v>
       </c>
       <c r="C722" t="inlineStr">
         <is>
@@ -14149,10 +14161,10 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B723" t="n">
-        <v>4470.735509064863</v>
+        <v>4494.545311298068</v>
       </c>
       <c r="C723" t="inlineStr">
         <is>
@@ -14172,10 +14184,10 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B724" t="n">
-        <v>4480.383655013275</v>
+        <v>4562.098597540023</v>
       </c>
       <c r="C724" t="inlineStr">
         <is>
@@ -14195,10 +14207,10 @@
     </row>
     <row r="725">
       <c r="A725" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B725" t="n">
-        <v>4494.545311298068</v>
+        <v>4674.68740794328</v>
       </c>
       <c r="C725" t="inlineStr">
         <is>
@@ -14218,10 +14230,10 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B726" t="n">
-        <v>4562.098597540023</v>
+        <v>4805.290428011061</v>
       </c>
       <c r="C726" t="inlineStr">
         <is>
@@ -14241,10 +14253,10 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B727" t="n">
-        <v>4674.68740794328</v>
+        <v>4922.382790830448</v>
       </c>
       <c r="C727" t="inlineStr">
         <is>
@@ -14264,10 +14276,10 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B728" t="n">
-        <v>4805.290428011061</v>
+        <v>5071.000020562749</v>
       </c>
       <c r="C728" t="inlineStr">
         <is>
@@ -14287,10 +14299,10 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="B729" t="n">
-        <v>4922.382790830448</v>
+        <v>5411.009600485539</v>
       </c>
       <c r="C729" t="inlineStr">
         <is>
@@ -14310,10 +14322,10 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B730" t="n">
-        <v>5071.000020562749</v>
+        <v>5498.440635322828</v>
       </c>
       <c r="C730" t="inlineStr">
         <is>
@@ -14333,10 +14345,10 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B731" t="n">
-        <v>5411.009600485539</v>
+        <v>5726.732781842416</v>
       </c>
       <c r="C731" t="inlineStr">
         <is>
@@ -14356,10 +14368,10 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="B732" t="n">
-        <v>5498.440635322828</v>
+        <v>5829.307075648131</v>
       </c>
       <c r="C732" t="inlineStr">
         <is>
@@ -14379,10 +14391,10 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B733" t="n">
-        <v>5726.732781842416</v>
+        <v>6148.980360227109</v>
       </c>
       <c r="C733" t="inlineStr">
         <is>
@@ -14402,10 +14414,10 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B734" t="n">
-        <v>5829.307075648131</v>
+        <v>6286.409996588172</v>
       </c>
       <c r="C734" t="inlineStr">
         <is>
@@ -14425,10 +14437,10 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B735" t="n">
-        <v>6148.980360227109</v>
+        <v>6088.232477487802</v>
       </c>
       <c r="C735" t="inlineStr">
         <is>
@@ -14448,10 +14460,10 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B736" t="n">
-        <v>6286.409996588172</v>
+        <v>5974.703647450409</v>
       </c>
       <c r="C736" t="inlineStr">
         <is>
@@ -14471,10 +14483,10 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B737" t="n">
-        <v>6088.232477487802</v>
+        <v>6155.951428738189</v>
       </c>
       <c r="C737" t="inlineStr">
         <is>
@@ -14494,10 +14506,10 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B738" t="n">
-        <v>5974.703647450409</v>
+        <v>6389.980157324025</v>
       </c>
       <c r="C738" t="inlineStr">
         <is>
@@ -14517,10 +14529,10 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B739" t="n">
-        <v>6155.951428738189</v>
+        <v>6480.60404796792</v>
       </c>
       <c r="C739" t="inlineStr">
         <is>
@@ -14540,10 +14552,10 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B740" t="n">
-        <v>6389.980157324025</v>
+        <v>6576.705206727648</v>
       </c>
       <c r="C740" t="inlineStr">
         <is>
@@ -14563,10 +14575,10 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B741" t="n">
-        <v>6480.60404796792</v>
+        <v>6650.897293024009</v>
       </c>
       <c r="C741" t="inlineStr">
         <is>
@@ -14586,10 +14598,10 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B742" t="n">
-        <v>6576.705206727648</v>
+        <v>6757.455054550329</v>
       </c>
       <c r="C742" t="inlineStr">
         <is>
@@ -14609,10 +14621,10 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B743" t="n">
-        <v>6650.897293024009</v>
+        <v>7415.225161916111</v>
       </c>
       <c r="C743" t="inlineStr">
         <is>
@@ -14625,52 +14637,6 @@
         </is>
       </c>
       <c r="E743" t="inlineStr">
-        <is>
-          <t>index_1930=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="744">
-      <c r="A744" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B744" t="n">
-        <v>6757.455054550329</v>
-      </c>
-      <c r="C744" t="inlineStr">
-        <is>
-          <t>S210-B</t>
-        </is>
-      </c>
-      <c r="D744" t="inlineStr">
-        <is>
-          <t>JASTRAM_1977_T2_PLUS_ONS_PLLU</t>
-        </is>
-      </c>
-      <c r="E744" t="inlineStr">
-        <is>
-          <t>index_1930=100</t>
-        </is>
-      </c>
-    </row>
-    <row r="745">
-      <c r="A745" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B745" t="n">
-        <v>7415.225161916111</v>
-      </c>
-      <c r="C745" t="inlineStr">
-        <is>
-          <t>S210-B</t>
-        </is>
-      </c>
-      <c r="D745" t="inlineStr">
-        <is>
-          <t>JASTRAM_1977_T2_PLUS_ONS_PLLU</t>
-        </is>
-      </c>
-      <c r="E745" t="inlineStr">
         <is>
           <t>index_1930=100</t>
         </is>
@@ -14688,7 +14654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -14710,7 +14676,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t># S210 -- US and UK Wholesale Price Indexes, 1780-2025 (Fig 2.10, log scale)</t>
+          <t># S210 -- US and UK Wholesale Price Indexes, 1780-2026 (Fig 2.8, log scale)</t>
         </is>
       </c>
     </row>
@@ -14830,7 +14796,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>In Shaikh (2016) the series appears as **Figure 2.10** in Chapter 2 ("The Wealth of Nations: A Long View").</t>
+          <t>In Shaikh (2016) the series appears as **Figure 2.8** in Chapter 2 ("Turbulent Trends and Hidden Structures").</t>
         </is>
       </c>
     </row>
@@ -14870,113 +14836,109 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
+          <t>The shipped chopped carries **two subseries (A = US, B = UK)**; the forward extensions are **folded into A and B** (there is no separate lettered extension subseries):</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| **S210-A** | 1780-2010 | Jastram (1977) T7 (US WPI) + BLS PPI extension (WPS-&gt;WPU) | Index 1930=100 | salvaged via CD2 S023 |</t>
+          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| **S210-B** | 1780-2010 | Jastram (1977) T2 (UK WPI) + ONS PLLU extension | Index 1930=100 | salvaged via CD2 S023 |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>| **S210-C** | 2011-2025 | FRED WPU00000000 (PPI All Commodities, US extension) | Index 1982=100 | FRED API |</t>
+          <t>| **S210-A** | 1780-2026 | Jastram (1977) T7 (US WPI) + BLS PPI extension (WPS-&gt;WPU) — `JASTRAM_1977_T7_PLUS_BLS_PPI_EXT` | Index 1930=100 | salvaged via CD2 S023; BLS PPI growth-rate splice onto the 1930=100 basis |</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>| **S210-B** | 1780-2022 | Jastram (1977) T2 (UK WPI) + **ONS PLLU** extension — `JASTRAM_1977_T2_PLUS_ONS_PLLU` | Index 1930=100 | salvaged via CD2 S023; ONS PLLU (Price Index of UK Output of Mfg Goods) growth-rate splice onto the 1930=100 basis |</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>**S210-C folded into S210-A (SWEEP-ch02-04).** An earlier draft declared a separate `S210-C` for the US FRED (`WPU00000000`) extension to 2025; the shipped chopped instead **folds the US extension into S210-A** (carried to 2026 under the `JASTRAM_1977_T7_PLUS_BLS_PPI_EXT` source_id), so no standalone S210-C ships. (Corrected 2026-07-02, campaign DF-2.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>## 4. Construction</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>`composite` construction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1. No Appendix 2 chopped table for WPI; CD2 S023 (which itself replicates Jastram + extensions) used as canonical book replica per decision 0005.</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2. Phase 4 substitution: BLS WPS00000000 frozen 1974 -&gt; use WPU00000000 for post-1974 US extension.</t>
+          <t>`composite` construction.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>3. Phase 4 URL update: NBER macrohistory -&gt; https://www.nber.org/research/data/nber-macrohistory-database.</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4. Extension currently US-only via FRED; UK extension via ONS PLLU deferred (transient 502 on specific page).</t>
+          <t>1. No Appendix 2 chopped table for WPI; CD2 S023 (which itself replicates Jastram + extensions) used as canonical book replica per decision 0005.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2. Phase 4 substitution: BLS WPS00000000 frozen 1974 -&gt; use WPU00000000 for post-1974 US extension.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>3. Phase 4 URL update: NBER macrohistory -&gt; https://www.nber.org/research/data/nber-macrohistory-database.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4. **Both country extensions ship (ONS-502 deferral resolved).** The shipped chopped extends S210-A (US) to **2026** via the BLS PPI splice and S210-B (UK) to **2022** via the **ONS PLLU** growth-rate splice — both folded into their book subseries. The earlier "UK extension deferred (transient 502)" limitation no longer applies to what ships. (Note: the L01_S210 / P02_S210 *code* still reflect the older path — US-only extension emitted as a separate S210-C via FRED and a "UK requires ONS PLLU, US-only continuation" diagnostic — which diverges from the shipped chopped. Flagged for the code owner; DF-2 does not touch code this wave.)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>- **Book period**: 1780-2010</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>- **Extension period**: 2011-2025</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
@@ -14986,44 +14948,44 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>- **Book period**: 1780-2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>- **Extension period (shipped)**: US (S210-A) 2011-2026; UK (S210-B) 2011-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>## 6. Units</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Index, 1930 = 100 (log scale on figure)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-    </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1. Canonical source not in chopped store; CD2 replica used (decision 0005).</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2. UK extension incomplete (ONS PLLU specific URL transient 502); document in EPR.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
@@ -15033,306 +14995,323 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>1. Canonical source not in chopped store; CD2 replica used (decision 0005).</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2. UK extension shipped to 2022 via ONS PLLU (the earlier transient-502 deferral is resolved in what ships). The UK line ends at 2022 vs the US line at 2026 simply because ONS PLLU's last available annual observation is 2022; this is a data-availability boundary, not a deferral.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.10</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>- Knowledge Base: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json`</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>- Predecessor (CD2): see registry `predecessor_ids` block.</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>- Book reference: Shaikh (2016), Ch. 2, Figure 2.8</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- Knowledge Base: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json`</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>- Predecessor (CD2): see registry `predecessor_ids` block.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>- **Tolerance**: +/- 1.0% per year (per playbook).</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: +/- 1.0% per year (per playbook).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>- **Expected MAE** (vs salvaged book truth): &lt; 0.5% when source data is pulled directly from the chopped table.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4">
+    <row r="76">
+      <c r="A76" s="4">
         <f>== EPR: S210_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t># S210 -- Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>**Series**: S210 -- US and UK Wholesale Price Indexes, 1780-2025 (Fig 2.10, log scale)</t>
-        </is>
-      </c>
-    </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t># S210 -- Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `composite`</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>**Extension status**: `feasible_with_substitute`</t>
+          <t>**Series**: S210 -- US and UK Wholesale Price Indexes, 1780-2026 (Fig 2.8, log scale)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Phase**: 6 (Extension)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave2-ch2</t>
+          <t>**Construction classification**: `composite`</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>**Related**: `S210_DPR.md`, `Technical/research/S210_research.json`</t>
+          <t>**Extension status**: `feasible_with_substitute`</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>**Author**: opus-subagent-wave2-ch2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>**Related**: `S210_DPR.md`, `Technical/research/S210_research.json`</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>---</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>## 1. Classification</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Per the playbook content-type rule, S210 is classified `composite`. Extension recipe applied: per the Anu framework rule on lazy splices, this dictates the extension method below.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>## 2. Method</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>BLS WPU00000000 for US; UK extension deferred until ONS PLLU page stabilizes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-    </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>BLS WPU00000000 (US) folded into S210-A, spliced to 2026; ONS PLLU (UK) folded into S210-B, spliced to 2022. Both extensions ship in the chopped (the earlier ONS-502 deferral is resolved in what ships). Both are growth-rate splices onto Jastram's 1930=100 basis, not proxy substitutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>## 3. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>WPU substitutes for frozen WPS post-1974 -- direct BLS successor under same program, not a proxy.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>## 4. No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>No synthetic, interpolated, or placeholder values are introduced. Where the API returns NaN, the NaN propagates to the published series.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>## 5. Failure-mode table</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-    </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>| Failure | Detection | Action |</t>
-        </is>
-      </c>
+      <c r="A104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>## 5. Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>| API key not set | `S00_config.have_key` returns False | Loader returns `degraded`; processor publishes book period only; registry stamped `extension_status: api_key_missing` |</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>| API non-200 | `S00_apis._retry_get` raises after 3 retries | Same degradation as above |</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>| Overlap year NaN | Processor checks pre-splice | Walk back overlap year (e.g. 2010 -&gt; 2009 -&gt; 2008); fail hard if no valid overlap in 5-year window |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>| Source URL discontinued | Phase 4 adequacy URL check | EPR documents the substitute (see section 3) |</t>
+          <t>| API key not set | `S00_config.have_key` returns False | Loader returns `degraded`; processor publishes book period only; registry stamped `extension_status: api_key_missing` |</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>| API non-200 | `S00_apis._retry_get` raises after 3 retries | Same degradation as above |</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>| Overlap year NaN | Processor checks pre-splice | Walk back overlap year (e.g. 2010 -&gt; 2009 -&gt; 2008); fail hard if no valid overlap in 5-year window |</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>| Source URL discontinued | Phase 4 adequacy URL check | EPR documents the substitute (see section 3) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>## 6. CD2 divergence pre-disclosure</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>CD2's predecessor series may diverge from S210 due to (a) different extension anchor, (b) different proxy selection, or (c) a different vintage of the underlying source. Divergence is reported informationally in V03 and never causes a FAIL.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>## 7. Extension status</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>Current: `feasible_with_substitute`. See DPR caveats for rationale.</t>
         </is>
@@ -15648,7 +15627,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T23:19:14.289059+00:00</t>
+          <t>2026-07-02T06:21:16.925360+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S210_extenbook.xlsx
+++ b/extenbooks/S210_extenbook.xlsx
@@ -15627,7 +15627,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:21:16.925360+00:00</t>
+          <t>2026-07-11T03:44:24.367692+00:00</t>
         </is>
       </c>
     </row>
@@ -15642,11 +15642,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15669,6 +15669,114 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.2 figure; book_period_validated; real data present in chopped CSV; KB-verified.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>index_1930=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
